--- a/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T2509_W0058F0001T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>18.36474862163032</v>
+        <v>2.984271651014927</v>
       </c>
       <c r="D2" t="n">
-        <v>19.11154014961622</v>
+        <v>3.105625274312636</v>
       </c>
       <c r="E2" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F2" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>64.96211301115439</v>
+        <v>10.55634336431259</v>
       </c>
       <c r="D3" t="n">
-        <v>65.52081960774282</v>
+        <v>10.64713318625821</v>
       </c>
       <c r="E3" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F3" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>72.89955071072518</v>
+        <v>11.84617699049284</v>
       </c>
       <c r="D4" t="n">
-        <v>73.37379000035335</v>
+        <v>11.92324087505742</v>
       </c>
       <c r="E4" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F4" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>48.50009154128727</v>
+        <v>7.881264875459181</v>
       </c>
       <c r="D5" t="n">
-        <v>48.78552904247653</v>
+        <v>7.927648469402436</v>
       </c>
       <c r="E5" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F5" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.78069170221053</v>
+        <v>7.439362401609212</v>
       </c>
       <c r="D6" t="n">
-        <v>46.55808713858438</v>
+        <v>7.565689160019963</v>
       </c>
       <c r="E6" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F6" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>31.10790471562299</v>
+        <v>5.055034516288736</v>
       </c>
       <c r="D7" t="n">
-        <v>31.40682585028975</v>
+        <v>5.103609200672085</v>
       </c>
       <c r="E7" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F7" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>6.131438202359324</v>
+        <v>0.9963587078833902</v>
       </c>
       <c r="D8" t="n">
-        <v>6.186647240656519</v>
+        <v>1.005330176606684</v>
       </c>
       <c r="E8" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F8" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>40.99377077946761</v>
+        <v>6.661487751663487</v>
       </c>
       <c r="D9" t="n">
-        <v>40.56362315306183</v>
+        <v>6.591588762372547</v>
       </c>
       <c r="E9" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F9" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>50.33197193393473</v>
+        <v>8.178945439264394</v>
       </c>
       <c r="D10" t="n">
-        <v>49.7718180151176</v>
+        <v>8.087920427456611</v>
       </c>
       <c r="E10" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F10" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87773204344181</v>
+        <v>5.342631457059294</v>
       </c>
       <c r="D11" t="n">
-        <v>32.09940006241813</v>
+        <v>5.216152510142946</v>
       </c>
       <c r="E11" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F11" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.63814548710381</v>
+        <v>6.116198641654369</v>
       </c>
       <c r="D12" t="n">
-        <v>36.89610655359462</v>
+        <v>5.995617314959126</v>
       </c>
       <c r="E12" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F12" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>40.18511584854409</v>
+        <v>6.530081325388414</v>
       </c>
       <c r="D13" t="n">
-        <v>39.45340364143949</v>
+        <v>6.411178091733918</v>
       </c>
       <c r="E13" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F13" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>50.21461676224932</v>
+        <v>8.159875223865514</v>
       </c>
       <c r="D14" t="n">
-        <v>49.6224437004462</v>
+        <v>8.063647101322509</v>
       </c>
       <c r="E14" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F14" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>56.52285831492218</v>
+        <v>9.184964476174855</v>
       </c>
       <c r="D15" t="n">
-        <v>55.80128807755818</v>
+        <v>9.067709312603204</v>
       </c>
       <c r="E15" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F15" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>52.50691367253182</v>
+        <v>8.532373471786421</v>
       </c>
       <c r="D16" t="n">
-        <v>51.74976608244617</v>
+        <v>8.409336988397504</v>
       </c>
       <c r="E16" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F16" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>3.79845973624268</v>
+        <v>0.6172497071394355</v>
       </c>
       <c r="D17" t="n">
-        <v>3.923671761623829</v>
+        <v>0.6375966612638722</v>
       </c>
       <c r="E17" t="n">
-        <v>18.54642283731999</v>
+        <v>3.013793711064499</v>
       </c>
       <c r="F17" t="n">
-        <v>18.50927971130237</v>
+        <v>3.007757953086636</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
